--- a/diseases/d003/2005-2009.xlsx
+++ b/diseases/d003/2005-2009.xlsx
@@ -1169,6 +1169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1710,6 +1715,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1858,6 +1868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2006,6 +2021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2154,6 +2174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2302,6 +2327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2450,6 +2480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2598,6 +2633,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2746,6 +2786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2894,6 +2939,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3042,6 +3092,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3190,6 +3245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3731,6 +3791,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4269,6 +4334,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4417,6 +4487,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4562,6 +4637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4710,6 +4790,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4855,6 +4940,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5003,6 +5093,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5148,6 +5243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5296,6 +5396,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5441,6 +5546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5589,6 +5699,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5734,6 +5849,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5882,6 +6002,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6027,6 +6152,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6175,6 +6305,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6320,6 +6455,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6468,6 +6608,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6613,6 +6758,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6761,6 +6911,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6906,6 +7061,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7054,6 +7214,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7199,6 +7364,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7347,6 +7517,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7492,6 +7667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8033,6 +8213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8571,6 +8756,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8719,6 +8909,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8864,6 +9059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9012,6 +9212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9157,6 +9362,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9305,6 +9515,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9450,6 +9665,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9598,6 +9818,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9743,6 +9968,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9891,6 +10121,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10036,6 +10271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10184,6 +10424,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10329,6 +10574,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10477,6 +10727,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10622,6 +10877,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10770,6 +11030,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10915,6 +11180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11063,6 +11333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11208,6 +11483,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11356,6 +11636,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11501,6 +11786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11649,6 +11939,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11794,6 +12089,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12335,6 +12635,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12873,6 +13178,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13021,6 +13331,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13166,6 +13481,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13314,6 +13634,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13459,6 +13784,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13607,6 +13937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13752,6 +14087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13900,6 +14240,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14045,6 +14390,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14193,6 +14543,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14338,6 +14693,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14486,6 +14846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14631,6 +14996,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14779,6 +15149,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14924,6 +15299,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15072,6 +15452,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15217,6 +15602,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15365,6 +15755,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15510,6 +15905,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15658,6 +16058,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15803,6 +16208,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15951,6 +16361,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16096,6 +16511,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16637,6 +17057,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17175,6 +17600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17323,6 +17753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17468,6 +17903,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17616,6 +18056,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17761,6 +18206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17909,6 +18359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18054,6 +18509,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18202,6 +18662,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18347,6 +18812,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18495,6 +18965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18640,6 +19115,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18788,6 +19268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18933,6 +19418,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19081,6 +19571,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19226,6 +19721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19374,6 +19874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19519,6 +20024,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19667,6 +20177,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19812,6 +20327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19960,6 +20480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20105,6 +20630,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20253,6 +20783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20396,6 +20931,11 @@
       <c r="S129" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">

--- a/diseases/d003/2005-2009.xlsx
+++ b/diseases/d003/2005-2009.xlsx
@@ -1299,6 +1299,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SARS_ANNUAL</t>
@@ -1316,7 +1321,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1327,6 +1337,11 @@
       <c r="AT5" t="n">
         <v>1</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -1349,22 +1364,22 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1391,17 +1406,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1426,12 +1441,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2005-02-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2005-02</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1440,69 +1455,165 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Córónaveirulungnabólga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1675,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2005-03-01</t>
+          <t>2005-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2005-03</t>
+          <t>2005-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1702,12 +1813,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2005-04-01</t>
+          <t>2005-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2005-04</t>
+          <t>2005-03</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1840,12 +1951,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2005-05-01</t>
+          <t>2005-04-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2005-05</t>
+          <t>2005-04</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1978,12 +2089,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2005-06-01</t>
+          <t>2005-05-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2005-06</t>
+          <t>2005-05</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2116,12 +2227,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2005-07-01</t>
+          <t>2005-06-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2005-07</t>
+          <t>2005-06</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2254,12 +2365,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2005-08-01</t>
+          <t>2005-07-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2005-08</t>
+          <t>2005-07</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2392,12 +2503,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
+          <t>2005-08-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2005-09</t>
+          <t>2005-08</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2530,12 +2641,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2005-10-01</t>
+          <t>2005-09-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2005-10</t>
+          <t>2005-09</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2668,12 +2779,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2005-11-01</t>
+          <t>2005-10-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2005-11</t>
+          <t>2005-10</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2806,12 +2917,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-11-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2005-12</t>
+          <t>2005-11</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2914,12 +3025,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2944,12 +3055,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2005-12-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2005-12</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -2958,90 +3069,69 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3158,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3117,98 +3207,23 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Severe Acute Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN18" t="b">
-        <v>1</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -3302,17 +3317,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3351,69 +3366,165 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Severe Acute Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3556,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3489,22 +3600,20 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -3512,52 +3621,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
+      <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3694,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3636,63 +3741,87 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3719,17 +3848,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3754,12 +3883,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2006-02-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3768,69 +3897,165 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Córónaveirulungnabólga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3892,12 +4117,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2006-02-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4027,12 +4252,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2006-03-01</t>
+          <t>2006-02-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4165,12 +4390,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2006-03-01</t>
+          <t>2006-02-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4300,12 +4525,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2006-04-01</t>
+          <t>2006-03-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4438,12 +4663,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2006-04-01</t>
+          <t>2006-03-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4573,12 +4798,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2006-05-01</t>
+          <t>2006-04-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4711,12 +4936,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2006-05-01</t>
+          <t>2006-04-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -4846,12 +5071,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
+          <t>2006-05-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -4984,12 +5209,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
+          <t>2006-05-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5119,12 +5344,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2006-07-01</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5257,12 +5482,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2006-07-01</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5392,12 +5617,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2006-07-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5530,12 +5755,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2006-07-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5665,12 +5890,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5803,12 +6028,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -5938,12 +6163,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2006-10-01</t>
+          <t>2006-09-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6076,12 +6301,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2006-10-01</t>
+          <t>2006-09-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6211,12 +6436,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2006-11-01</t>
+          <t>2006-10-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6349,12 +6574,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2006-11-01</t>
+          <t>2006-10-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6484,12 +6709,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-11-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6622,12 +6847,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-11-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6727,12 +6952,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6757,12 +6982,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-12-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -6771,90 +6996,69 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6881,17 +7085,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6916,12 +7120,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-12-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -6930,165 +7134,66 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Severe Acute Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R45" t="n">
+        <v>0</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN45" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7225,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7164,69 +7269,90 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7253,17 +7379,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7302,12 +7428,34 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Severe Acute Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7315,6 +7463,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7322,55 +7528,65 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
         </is>
       </c>
       <c r="AT47" t="n">
         <v>1</v>
       </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7402,12 +7618,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7444,6 +7660,9 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
@@ -7470,42 +7689,42 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7537,12 +7756,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7567,12 +7786,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7581,69 +7800,90 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -7670,17 +7910,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7705,12 +7945,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -7719,66 +7959,165 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="R50" t="n">
-        <v>0</v>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Córónaveirulungnabólga</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN50" t="b">
+        <v>1</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -7810,12 +8149,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7840,21 +8179,18 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
@@ -7881,42 +8217,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7948,12 +8284,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7978,18 +8314,21 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
@@ -8016,42 +8355,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8083,12 +8422,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8113,21 +8452,18 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
@@ -8154,42 +8490,42 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8221,12 +8557,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8251,18 +8587,21 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
@@ -8289,42 +8628,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8695,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8386,21 +8725,18 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
@@ -8427,42 +8763,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8494,12 +8830,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8524,18 +8860,21 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
@@ -8562,42 +8901,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8629,12 +8968,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8659,21 +8998,18 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N57" t="n">
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
@@ -8700,42 +9036,42 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8767,12 +9103,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8797,18 +9133,21 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
@@ -8835,42 +9174,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8902,12 +9241,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8932,21 +9271,18 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
@@ -8973,42 +9309,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9040,12 +9376,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9070,18 +9406,21 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
@@ -9108,42 +9447,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9175,12 +9514,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9205,21 +9544,18 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
@@ -9246,42 +9582,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9313,12 +9649,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9343,18 +9679,21 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
@@ -9381,42 +9720,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9448,12 +9787,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9478,21 +9817,18 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
@@ -9519,42 +9855,42 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9586,12 +9922,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9616,18 +9952,21 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
@@ -9654,42 +9993,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9721,12 +10060,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9751,21 +10090,18 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
@@ -9792,42 +10128,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9859,12 +10195,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9889,18 +10225,21 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
@@ -9927,42 +10266,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9994,12 +10333,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10024,21 +10363,18 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
@@ -10065,42 +10401,42 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10132,12 +10468,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10162,18 +10498,21 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
@@ -10200,42 +10539,42 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10267,12 +10606,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10297,21 +10636,18 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
@@ -10338,42 +10674,42 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10741,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10435,18 +10771,21 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
@@ -10473,42 +10812,42 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10540,12 +10879,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10570,12 +10909,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -10587,87 +10926,63 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10694,17 +11009,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -10729,12 +11044,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -10743,165 +11058,69 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Severe Acute Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN72" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10933,12 +11152,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10963,21 +11182,18 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N73" t="n">
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
@@ -11004,42 +11220,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11071,12 +11287,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11118,9 +11334,14 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -11135,55 +11356,65 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
         </is>
       </c>
       <c r="AT74" t="n">
         <v>1</v>
       </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11210,17 +11441,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11259,66 +11490,165 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="R75" t="n">
-        <v>0</v>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Severe Acute Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11380,12 +11710,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -11488,12 +11818,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11518,12 +11848,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -11535,63 +11865,87 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11618,17 +11972,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11653,12 +12007,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -11667,69 +12021,165 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Córónaveirulungnabólga</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN78" t="b">
+        <v>1</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11791,12 +12241,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -11926,12 +12376,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12064,12 +12514,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12199,12 +12649,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -12337,12 +12787,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -12472,12 +12922,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -12610,12 +13060,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -12745,12 +13195,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -12883,12 +13333,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -13018,12 +13468,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -13156,12 +13606,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -13291,12 +13741,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -13429,12 +13879,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -13564,12 +14014,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -13702,12 +14152,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -13837,12 +14287,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -13975,12 +14425,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N95" t="n">
@@ -14110,12 +14560,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -14248,12 +14698,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -14353,12 +14803,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -14383,12 +14833,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -14397,90 +14847,69 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14507,17 +14936,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -14542,12 +14971,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -14556,165 +14985,66 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Severe Acute Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R99" t="n">
+        <v>0</v>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD99" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE99" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF99" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG99" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN99" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14776,12 +15106,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -14884,12 +15214,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -14914,12 +15244,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -14931,19 +15261,14 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
@@ -14951,52 +15276,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
+      <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15028,12 +15349,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15075,63 +15396,87 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15158,17 +15503,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -15193,12 +15538,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N103" t="n">
@@ -15207,69 +15552,165 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0</v>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Severe Acute Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15301,12 +15742,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -15331,18 +15772,21 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N104" t="n">
         <v>0</v>
       </c>
       <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
@@ -15369,42 +15813,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15436,12 +15880,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -15466,12 +15910,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -15480,69 +15924,90 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -15569,17 +16034,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -15604,12 +16069,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N106" t="n">
@@ -15618,66 +16083,165 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="R106" t="n">
-        <v>0</v>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Córónaveirulungnabólga</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>1</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -15709,12 +16273,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -15739,21 +16303,18 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N107" t="n">
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
@@ -15780,42 +16341,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15847,12 +16408,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -15877,18 +16438,21 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N108" t="n">
         <v>0</v>
       </c>
       <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
@@ -15915,42 +16479,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15982,12 +16546,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -16012,21 +16576,18 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N109" t="n">
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
@@ -16053,42 +16614,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16120,12 +16681,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -16150,18 +16711,21 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N110" t="n">
         <v>0</v>
       </c>
       <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
@@ -16188,42 +16752,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16255,12 +16819,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -16285,21 +16849,18 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N111" t="n">
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
@@ -16326,42 +16887,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16393,12 +16954,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -16423,18 +16984,21 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N112" t="n">
         <v>0</v>
       </c>
       <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
@@ -16461,42 +17025,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16528,12 +17092,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -16558,21 +17122,18 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N113" t="n">
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
@@ -16599,42 +17160,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16666,12 +17227,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -16696,18 +17257,21 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N114" t="n">
         <v>0</v>
       </c>
       <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
@@ -16734,42 +17298,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16801,12 +17365,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -16831,21 +17395,18 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N115" t="n">
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
@@ -16872,42 +17433,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16939,12 +17500,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -16969,18 +17530,21 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N116" t="n">
         <v>0</v>
       </c>
       <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
@@ -17007,42 +17571,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17074,12 +17638,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -17104,21 +17668,18 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N117" t="n">
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
@@ -17145,42 +17706,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17212,12 +17773,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -17242,18 +17803,21 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N118" t="n">
         <v>0</v>
       </c>
       <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
@@ -17280,42 +17844,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17347,12 +17911,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -17377,21 +17941,18 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N119" t="n">
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
@@ -17418,42 +17979,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17485,12 +18046,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -17515,18 +18076,21 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N120" t="n">
         <v>0</v>
       </c>
       <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
@@ -17553,42 +18117,42 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17620,12 +18184,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -17650,21 +18214,18 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N121" t="n">
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
@@ -17691,42 +18252,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17758,12 +18319,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -17788,18 +18349,21 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N122" t="n">
         <v>0</v>
       </c>
       <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
@@ -17826,42 +18390,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17893,12 +18457,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -17923,21 +18487,18 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N123" t="n">
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
@@ -17964,42 +18525,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18031,12 +18592,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -18061,18 +18622,21 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N124" t="n">
         <v>0</v>
       </c>
       <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
@@ -18099,40 +18663,721 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW124" t="inlineStr">
+      <c r="AW125" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
+      <c r="AX125" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY124" t="inlineStr">
+      <c r="AY125" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
+      <c r="AZ125" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA124" t="inlineStr">
+      <c r="BA125" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB124" t="inlineStr">
+      <c r="BB125" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC124" t="inlineStr">
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -18264,7 +19509,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -18284,7 +19529,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -18294,7 +19539,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d003/2005-2009.xlsx
+++ b/diseases/d003/2005-2009.xlsx
@@ -1164,6 +1164,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1176,12 +1181,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1695,6 +1710,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1707,12 +1727,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1833,6 +1863,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1845,12 +1880,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1971,6 +2016,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1983,12 +2033,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2109,6 +2169,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2121,12 +2186,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2247,6 +2322,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2259,12 +2339,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2385,6 +2475,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2397,12 +2492,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2523,6 +2628,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2535,12 +2645,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2661,6 +2781,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2673,12 +2798,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2799,6 +2934,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2811,12 +2951,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2937,6 +3087,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2949,12 +3104,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3075,6 +3240,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3087,12 +3257,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3606,6 +3786,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3618,12 +3803,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -4134,6 +4329,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4146,12 +4346,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4272,6 +4482,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4284,12 +4499,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4407,6 +4632,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4419,12 +4649,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4545,6 +4785,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4557,12 +4802,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4680,6 +4935,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4692,12 +4952,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4818,6 +5088,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4830,12 +5105,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4953,6 +5238,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4965,12 +5255,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5091,6 +5391,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5103,12 +5408,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5226,6 +5541,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5238,12 +5558,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5364,6 +5694,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5376,12 +5711,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5499,6 +5844,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5511,12 +5861,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5637,6 +5997,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5649,12 +6014,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5772,6 +6147,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5784,12 +6164,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5910,6 +6300,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5922,12 +6317,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6045,6 +6450,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6057,12 +6467,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6183,6 +6603,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6195,12 +6620,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6318,6 +6753,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6330,12 +6770,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6456,6 +6906,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6468,12 +6923,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6591,6 +7056,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6603,12 +7073,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6729,6 +7209,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6741,12 +7226,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6864,6 +7359,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6876,12 +7376,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7002,6 +7512,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7014,12 +7529,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7137,6 +7662,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7149,12 +7679,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7668,6 +8208,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7680,12 +8225,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8196,6 +8751,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8208,12 +8768,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8334,6 +8904,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8346,12 +8921,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8469,6 +9054,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8481,12 +9071,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8607,6 +9207,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8619,12 +9224,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8742,6 +9357,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8754,12 +9374,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8880,6 +9510,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8892,12 +9527,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9015,6 +9660,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9027,12 +9677,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9153,6 +9813,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9165,12 +9830,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9288,6 +9963,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9300,12 +9980,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9426,6 +10116,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9438,12 +10133,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9561,6 +10266,11 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9573,12 +10283,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9699,6 +10419,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9711,12 +10436,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9834,6 +10569,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9846,12 +10586,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9972,6 +10722,11 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9984,12 +10739,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10107,6 +10872,11 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10119,12 +10889,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10245,6 +11025,11 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10257,12 +11042,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10380,6 +11175,11 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10392,12 +11192,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10518,6 +11328,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10530,12 +11345,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10653,6 +11478,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10665,12 +11495,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10791,6 +11631,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10803,12 +11648,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10926,6 +11781,11 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10938,12 +11798,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11064,6 +11934,11 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11076,12 +11951,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11199,6 +12084,11 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11211,12 +12101,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11730,6 +12630,11 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11742,12 +12647,22 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12258,6 +13173,11 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12270,12 +13190,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12396,6 +13326,11 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12408,12 +13343,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12531,6 +13476,11 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12543,12 +13493,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12669,6 +13629,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12681,12 +13646,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12804,6 +13779,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12816,12 +13796,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12942,6 +13932,11 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12954,12 +13949,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13077,6 +14082,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13089,12 +14099,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13215,6 +14235,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13227,12 +14252,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13350,6 +14385,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13362,12 +14402,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13488,6 +14538,11 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13500,12 +14555,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13623,6 +14688,11 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13635,12 +14705,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13761,6 +14841,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13773,12 +14858,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13896,6 +14991,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13908,12 +15008,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14034,6 +15144,11 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14046,12 +15161,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14169,6 +15294,11 @@
       <c r="R93" t="n">
         <v>0</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14181,12 +15311,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14307,6 +15447,11 @@
       <c r="R94" t="n">
         <v>0</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14319,12 +15464,22 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14442,6 +15597,11 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14454,12 +15614,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14580,6 +15750,11 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14592,12 +15767,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14715,6 +15900,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14727,12 +15917,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14853,6 +16053,11 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14865,12 +16070,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14988,6 +16203,11 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15000,12 +16220,22 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15126,6 +16356,11 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15138,12 +16373,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15261,6 +16506,11 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15273,12 +16523,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15792,6 +17052,11 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15804,12 +17069,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16320,6 +17595,11 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16332,12 +17612,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16458,6 +17748,11 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16470,12 +17765,22 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -16593,6 +17898,11 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16605,12 +17915,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16731,6 +18051,11 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16743,12 +18068,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -16866,6 +18201,11 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16878,12 +18218,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17004,6 +18354,11 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17016,12 +18371,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -17139,6 +18504,11 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17151,12 +18521,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -17277,6 +18657,11 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17289,12 +18674,22 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17412,6 +18807,11 @@
       <c r="R115" t="n">
         <v>0</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17424,12 +18824,22 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -17550,6 +18960,11 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17562,12 +18977,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -17685,6 +19110,11 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17697,12 +19127,22 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -17823,6 +19263,11 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17835,12 +19280,22 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -17958,6 +19413,11 @@
       <c r="R119" t="n">
         <v>0</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17970,12 +19430,22 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18096,6 +19566,11 @@
       <c r="R120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18108,12 +19583,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18231,6 +19716,11 @@
       <c r="R121" t="n">
         <v>0</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18243,12 +19733,22 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -18369,6 +19869,11 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18381,12 +19886,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -18504,6 +20019,11 @@
       <c r="R123" t="n">
         <v>0</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18516,12 +20036,22 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -18642,6 +20172,11 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18654,12 +20189,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -18777,6 +20322,11 @@
       <c r="R125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18789,12 +20339,22 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -18915,6 +20475,11 @@
       <c r="R126" t="n">
         <v>0</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18927,12 +20492,22 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19050,6 +20625,11 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19062,12 +20642,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19188,6 +20778,11 @@
       <c r="R128" t="n">
         <v>0</v>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19200,12 +20795,22 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -19323,6 +20928,11 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19335,12 +20945,22 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
